--- a/data/derived/stage0-intake.xlsx
+++ b/data/derived/stage0-intake.xlsx
@@ -27,7 +27,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -74,13 +76,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -246,7 +249,8 @@
     </comment>
     <comment ref="N1" authorId="0" shapeId="0">
       <text>
-        <t>Required by the schema, and may be left blank: a blank is reported as a gap, never filled in.</t>
+        <t>A date. The column is formatted as one, so typing 25/08/2026 is fine. If you type it as text, write it as 2026-08-25 — a slashed date that could be read either way round is refused, not guessed.
+Required by the schema, and may be left blank: a blank is reported as a gap, never filled in.</t>
       </text>
     </comment>
   </commentList>
@@ -313,7 +317,8 @@
     </comment>
     <comment ref="J1" authorId="0" shapeId="0">
       <text>
-        <t>Required by the schema, and may be left blank: a blank is reported as a gap, never filled in.</t>
+        <t>A date. The column is formatted as one, so typing 25/08/2026 is fine. If you type it as text, write it as 2026-08-25 — a slashed date that could be read either way round is refused, not guessed.
+Required by the schema, and may be left blank: a blank is reported as a gap, never filled in.</t>
       </text>
     </comment>
   </commentList>
@@ -386,7 +391,8 @@
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
-        <t>Required by the schema, and may be left blank: a blank is reported as a gap, never filled in.</t>
+        <t>A date. The column is formatted as one, so typing 25/08/2026 is fine. If you type it as text, write it as 2026-08-25 — a slashed date that could be read either way round is refused, not guessed.
+Required by the schema, and may be left blank: a blank is reported as a gap, never filled in.</t>
       </text>
     </comment>
   </commentList>
@@ -461,7 +467,8 @@
     </comment>
     <comment ref="L1" authorId="0" shapeId="0">
       <text>
-        <t>Required by the schema, and may be left blank: a blank is reported as a gap, never filled in.</t>
+        <t>A date. The column is formatted as one, so typing 25/08/2026 is fine. If you type it as text, write it as 2026-08-25 — a slashed date that could be read either way round is refused, not guessed.
+Required by the schema, and may be left blank: a blank is reported as a gap, never filled in.</t>
       </text>
     </comment>
   </commentList>
@@ -551,7 +558,8 @@
     </comment>
     <comment ref="N1" authorId="0" shapeId="0">
       <text>
-        <t>Required by the schema, and may be left blank: a blank is reported as a gap, never filled in.</t>
+        <t>A date. The column is formatted as one, so typing 25/08/2026 is fine. If you type it as text, write it as 2026-08-25 — a slashed date that could be read either way round is refused, not guessed.
+Required by the schema, and may be left blank: a blank is reported as a gap, never filled in.</t>
       </text>
     </comment>
   </commentList>
@@ -603,7 +611,8 @@
     </comment>
     <comment ref="H1" authorId="0" shapeId="0">
       <text>
-        <t>Required by the schema, and may be left blank: a blank is reported as a gap, never filled in.</t>
+        <t>A date. The column is formatted as one, so typing 25/08/2026 is fine. If you type it as text, write it as 2026-08-25 — a slashed date that could be read either way round is refused, not guessed.
+Required by the schema, and may be left blank: a blank is reported as a gap, never filled in.</t>
       </text>
     </comment>
   </commentList>
@@ -702,7 +711,8 @@
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
-        <t>Required by the schema, and may be left blank: a blank is reported as a gap, never filled in.</t>
+        <t>A date. The column is formatted as one, so typing 25/08/2026 is fine. If you type it as text, write it as 2026-08-25 — a slashed date that could be read either way round is refused, not guessed.
+Required by the schema, and may be left blank: a blank is reported as a gap, never filled in.</t>
       </text>
     </comment>
   </commentList>
@@ -763,7 +773,8 @@
     </comment>
     <comment ref="I1" authorId="0" shapeId="0">
       <text>
-        <t>Required by the schema, and may be left blank: a blank is reported as a gap, never filled in.</t>
+        <t>A date. The column is formatted as one, so typing 25/08/2026 is fine. If you type it as text, write it as 2026-08-25 — a slashed date that could be read either way round is refused, not guessed.
+Required by the schema, and may be left blank: a blank is reported as a gap, never filled in.</t>
       </text>
     </comment>
   </commentList>
@@ -1258,51 +1269,51 @@
     <col width="28" customWidth="1" min="6" max="6"/>
     <col width="28" customWidth="1" min="7" max="7"/>
     <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" style="4" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>given</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>must_not_infer</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>tier</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>explanation_required</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>caveats</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>approved_by</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>approved_date</t>
         </is>
@@ -1338,22 +1349,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>parent_id</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>conclusion</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>basis</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>kind</t>
         </is>
@@ -1388,56 +1399,56 @@
     <col width="34" customWidth="1" min="7" max="7"/>
     <col width="28" customWidth="1" min="8" max="8"/>
     <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" style="4" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>prohibited</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>kind</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>why</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>detectable_by</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>test_ref</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>related_questions</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>approved_by</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>approved_date</t>
         </is>
@@ -1768,76 +1779,76 @@
     <col width="28" customWidth="1" min="11" max="11"/>
     <col width="34" customWidth="1" min="12" max="12"/>
     <col width="28" customWidth="1" min="13" max="13"/>
-    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" style="4" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>question</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>asked_by</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>pilot_in_scope</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>expected_sources.required</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>expected_sources.supporting</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>expected_concepts</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>must_not_include</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>answer_shape</t>
         </is>
       </c>
-      <c r="K1" s="5" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>caveats</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>measured_by</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>approved_by</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>approved_date</t>
         </is>
@@ -1879,61 +1890,61 @@
     <col width="28" customWidth="1" min="8" max="8"/>
     <col width="28" customWidth="1" min="9" max="9"/>
     <col width="28" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" style="4" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>surface</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>source_ref</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>span.start</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>span.end</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>source_content_hash</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>resolves_to</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>approved_by</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>approved_date</t>
         </is>
@@ -1970,66 +1981,66 @@
     <col width="34" customWidth="1" min="9" max="9"/>
     <col width="28" customWidth="1" min="10" max="10"/>
     <col width="28" customWidth="1" min="11" max="11"/>
-    <col width="28" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" style="4" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>pref_label</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>alt_labels</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>not_labels</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>broader</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>narrower</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>related</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>definition_sources</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>legislative_basis</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="J1" s="6" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>approved_by</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>approved_date</t>
         </is>
@@ -2063,76 +2074,76 @@
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="28" customWidth="1" min="12" max="12"/>
     <col width="28" customWidth="1" min="13" max="13"/>
-    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" style="4" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>subject</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>predicate</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>object</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>source_ref</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>supporting_text</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>span.start</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>span.end</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>source_content_hash</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>tier</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>modality</t>
         </is>
       </c>
-      <c r="L1" s="5" t="inlineStr">
+      <c r="L1" s="6" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>approved_by</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>approved_date</t>
         </is>
@@ -2168,46 +2179,46 @@
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="28" customWidth="1" min="6" max="6"/>
     <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" style="4" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>query</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>uses_manual_terminology</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>irrelevant_but_tempting</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>must_exclude</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>approved_by</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>approved_date</t>
         </is>
@@ -2239,17 +2250,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>parent_id</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>ref</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>grade</t>
         </is>
@@ -2285,61 +2296,61 @@
     <col width="34" customWidth="1" min="8" max="8"/>
     <col width="28" customWidth="1" min="9" max="9"/>
     <col width="28" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" style="4" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>question</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>required_evidence</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>required_provisions</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>required_cases</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>qualifications_expected</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>authority_distinction_required</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>prohibited_conclusions</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>approved_by</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>approved_date</t>
         </is>
